--- a/InputData/fuels/FPIEBP/Fuel Prod Imp Exp Balancing Priorities.xlsx
+++ b/InputData/fuels/FPIEBP/Fuel Prod Imp Exp Balancing Priorities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\fuels\FPIEBP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iamho\Dropbox\Energy Innovation\InputData_Working\홍상현\fuels\FPIEBP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4E0A33-3857-4E42-99DE-F3DBB58130FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE14295-D8D7-4C63-8B3E-D545ACFA7EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18705" yWindow="1695" windowWidth="19470" windowHeight="20340" xr2:uid="{B505BEC9-7B7D-48ED-A025-9B3B4252ED08}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="28830" windowHeight="18770" activeTab="1" xr2:uid="{B505BEC9-7B7D-48ED-A025-9B3B4252ED08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -230,11 +230,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -242,7 +242,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -250,8 +250,15 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -302,7 +309,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -318,7 +325,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -615,14 +622,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290315BF-FDD8-4070-97AB-AF459B926789}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -630,90 +637,90 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
@@ -721,102 +728,103 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -828,13 +836,13 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" customWidth="1"/>
-    <col min="2" max="4" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="36.25" customWidth="1"/>
+    <col min="2" max="4" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>59</v>
       </c>
@@ -848,7 +856,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
@@ -862,35 +870,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
@@ -904,7 +912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
         <v>42</v>
       </c>
@@ -918,7 +926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
         <v>43</v>
       </c>
@@ -932,7 +940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
         <v>44</v>
       </c>
@@ -946,92 +954,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="9">
-        <v>3</v>
-      </c>
-      <c r="D9" s="9">
-        <v>2</v>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
       </c>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="9">
-        <v>1</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="9">
-        <v>1</v>
-      </c>
-      <c r="C11" s="9">
-        <v>3</v>
-      </c>
-      <c r="D11" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="9">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9">
-        <v>3</v>
-      </c>
-      <c r="D12" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="9">
-        <v>1</v>
-      </c>
-      <c r="C13" s="9">
-        <v>2</v>
-      </c>
-      <c r="D13" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="9">
-        <v>1</v>
-      </c>
-      <c r="C14" s="9">
-        <v>3</v>
-      </c>
-      <c r="D14" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="6" t="s">
         <v>51</v>
       </c>
@@ -1045,7 +1053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="6" t="s">
         <v>52</v>
       </c>
@@ -1059,63 +1067,63 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="9">
-        <v>1</v>
-      </c>
-      <c r="C17" s="9">
-        <v>3</v>
-      </c>
-      <c r="D17" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="9">
-        <v>2</v>
-      </c>
-      <c r="C18" s="9">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="9">
-        <v>1</v>
-      </c>
-      <c r="C19" s="9">
-        <v>3</v>
-      </c>
-      <c r="D19" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="9">
-        <v>1</v>
-      </c>
-      <c r="C20" s="9">
-        <v>3</v>
-      </c>
-      <c r="D20" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>57</v>
       </c>
@@ -1129,21 +1137,194 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B22" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC7F512-C22E-43DE-AB95-78A22CC2F565}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B3F07D4-B02D-4A72-80E7-3FA4A49A1B5A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A1F18D0-9CA2-4EBC-8E99-CC1E3887BC09}"/>
 </file>